--- a/data-manipulation-scripts/sheets-cleanup/sheets/EMBREAGEM SECUNDARIA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/EMBREAGEM SECUNDARIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -32,6 +32,12 @@
   </si>
   <si>
     <t>EMBREAGEM SECUNDARIA COMPLETA TMAC LEAD 110 2009 A 2015 TC1129</t>
+  </si>
+  <si>
+    <t>7898635122456</t>
+  </si>
+  <si>
+    <t>EMBREAGEM SSECUNDARIA COMPLETA CAWU PCX 2019</t>
   </si>
 </sst>
 </file>
@@ -92,7 +98,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -362,7 +368,9 @@
       <c r="C2" s="4">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>520.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -387,13 +395,40 @@
       <c r="Z2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
+      <c r="A3" s="3" t="s">
+        <v>7</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="7"/>
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>730.0</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
